--- a/artfynd/A 49737-2022 artfynd.xlsx
+++ b/artfynd/A 49737-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 49737-2022 artfynd.xlsx
+++ b/artfynd/A 49737-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -940,134 +940,6 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>68354690</v>
-      </c>
-      <c r="B4" t="n">
-        <v>104838</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>219955</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Slåttergubbe</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Arnica montana</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>Bredhällavägen, Karskruv, Sm</t>
-        </is>
-      </c>
-      <c r="Q4" t="n">
-        <v>518108.9748137452</v>
-      </c>
-      <c r="R4" t="n">
-        <v>6326552.788809819</v>
-      </c>
-      <c r="S4" t="n">
-        <v>10</v>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>Kronoberg</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>Uppvidinge</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>Småland</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>Nottebäck</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>2017-06-21</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>2017-06-21</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Vägkant</t>
-        </is>
-      </c>
-      <c r="AT4" t="inlineStr"/>
-      <c r="AW4" t="inlineStr">
-        <is>
-          <t>Örjan Fritz</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>Örjan Fritz</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 49737-2022 artfynd.xlsx
+++ b/artfynd/A 49737-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>68354718</v>
+        <v>594823</v>
       </c>
       <c r="B2" t="n">
-        <v>102161</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>105117</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,7 +705,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -723,17 +718,16 @@
           <t>blomning</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bredhällavägen, Karskruv, Sm</t>
+          <t>Karskruv, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>518108.9748137452</v>
+        <v>518075</v>
       </c>
       <c r="R2" t="n">
-        <v>6326552.788809819</v>
+        <v>6326573</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -760,22 +754,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2017-06-21</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2010-05-15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2017-06-21</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2010-05-31</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Observatör Thorsten Zaar</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,52 +776,52 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Artificiell miljö</t>
+        </is>
+      </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Vägkant</t>
+          <t>vägkant</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Örjan Fritz</t>
+          <t>Jonas Hedin</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Örjan Fritz</t>
+          <t>Via Jonas Hedin</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>90949279</v>
+        <v>68354718</v>
       </c>
       <c r="B3" t="n">
-        <v>104838</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>105117</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219955</v>
+        <v>1560</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Slåttergubbe</t>
+          <t>Spindelört</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Arnica montana</t>
+          <t>Thesium alpinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -850,16 +839,22 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Bredhällavägen, Karskruv, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>518109.5193174668</v>
+        <v>518109</v>
       </c>
       <c r="R3" t="n">
-        <v>6326552.791193254</v>
+        <v>6326553</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,29 +879,14 @@
           <t>Nottebäck</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>G-Upp-0463</t>
-        </is>
-      </c>
       <c r="Y3" t="inlineStr">
         <is>
           <t>2017-06-21</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2017-06-21</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -926,19 +906,911 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
+          <t>Örjan Fritz</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Örjan Fritz</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>68355065</v>
+      </c>
+      <c r="B4" t="n">
+        <v>97980</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>1895</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Strandlummer</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Lycopodiella inundata</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) Holub</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Karskruv, norr om Bredhällavägen, Sm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>518199</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6326645</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Uppvidinge</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Nottebäck</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2017-04-27</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2017-04-27</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Mycket sparsam</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Gammal grustäkt, fuktsvacka</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Örjan Fritz</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Örjan Fritz</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>68355047</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57144</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>102613</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Orre</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Lyrurus tetrix</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Karskruv, norr om Bredhällavägen, Sm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>518272</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6326698</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Uppvidinge</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Nottebäck</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2017-04-27</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2017-04-27</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Tallmosse</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Örjan Fritz</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Örjan Fritz</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>68354690</v>
+      </c>
+      <c r="B6" t="n">
+        <v>107908</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>219955</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Slåttergubbe</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Arnica montana</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Bredhällavägen, Karskruv, Sm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>518109</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6326553</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Uppvidinge</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Nottebäck</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2017-06-21</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2017-06-21</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Vägkant</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Örjan Fritz</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Örjan Fritz</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>90949279</v>
+      </c>
+      <c r="B7" t="n">
+        <v>107908</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>219955</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Slåttergubbe</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Arnica montana</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Bredhällavägen, Karskruv, Sm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>518110</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6326553</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Uppvidinge</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Nottebäck</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>G-Upp-0463</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2017-06-21</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2017-06-21</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Vägkant</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
           <t>Sofia Lund</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
+      <c r="AX7" t="inlineStr">
         <is>
           <t>Örjan Fritz</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr">
+      <c r="AY7" t="inlineStr">
         <is>
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>68355056</v>
+      </c>
+      <c r="B8" t="n">
+        <v>97987</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>224364</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Vanlig mattlummer</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum subsp. clavatum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Karskruv, norr om Bredhällavägen, Sm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>518186</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6326652</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Uppvidinge</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Nottebäck</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2017-04-27</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2017-04-27</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Gammal grustäkt</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Örjan Fritz</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Örjan Fritz</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>68355058</v>
+      </c>
+      <c r="B9" t="n">
+        <v>97987</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>224364</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Vanlig mattlummer</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum subsp. clavatum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Karskruv, norr om Bredhällavägen, Sm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>518188</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6326637</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Uppvidinge</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Nottebäck</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2017-04-27</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2017-04-27</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Gammal grustäkt</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Örjan Fritz</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Örjan Fritz</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>68355070</v>
+      </c>
+      <c r="B10" t="n">
+        <v>97987</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>224364</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Vanlig mattlummer</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum subsp. clavatum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Karskruv, norr om Bredhällavägen, Sm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>518206</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6326644</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Uppvidinge</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Nottebäck</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2017-04-27</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2017-04-27</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Gammal grustäkt, vägkant</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Örjan Fritz</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Örjan Fritz</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>68354695</v>
+      </c>
+      <c r="B11" t="n">
+        <v>102563</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>265350</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Vanligt jungfrulin</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Polygala vulgaris subsp. vulgaris</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Bredhällavägen, Karskruv, Sm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>518109</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6326553</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Uppvidinge</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Nottebäck</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2017-06-21</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2017-06-21</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Vägkant</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Örjan Fritz</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Örjan Fritz</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 49737-2022 artfynd.xlsx
+++ b/artfynd/A 49737-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -918,10 +918,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>68355065</v>
+        <v>135136908</v>
       </c>
       <c r="B4" t="n">
-        <v>97980</v>
+        <v>105196</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -929,48 +929,45 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1895</v>
+        <v>1560</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Strandlummer</t>
+          <t>Spindelört</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodiella inundata</t>
+          <t>Thesium alpinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Holub</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Karskruv, norr om Bredhällavägen, Sm</t>
+          <t>Karskruv, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>518199</v>
+        <v>518106</v>
       </c>
       <c r="R4" t="n">
-        <v>6326645</v>
+        <v>6326558</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -994,17 +991,27 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2017-04-27</t>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2017-04-27</t>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Mycket sparsam</t>
+          <t>Vändplats</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1013,82 +1020,78 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Gammal grustäkt, fuktsvacka</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Örjan Fritz</t>
+          <t>thorsten Zaar</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Örjan Fritz</t>
+          <t>thorsten Zaar</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>68355047</v>
+        <v>68355065</v>
       </c>
       <c r="B5" t="n">
-        <v>57144</v>
+        <v>97980</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102613</v>
+        <v>1895</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Strandlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Lycopodiella inundata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Holub</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Karskruv, norr om Bredhällavägen, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>518272</v>
+        <v>518199</v>
       </c>
       <c r="R5" t="n">
-        <v>6326698</v>
+        <v>6326645</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1120,6 +1123,11 @@
           <t>2017-04-27</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Mycket sparsam</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1131,7 +1139,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Tallmosse</t>
+          <t>Gammal grustäkt, fuktsvacka</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1149,59 +1157,59 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>68354690</v>
+        <v>68355047</v>
       </c>
       <c r="B6" t="n">
-        <v>107908</v>
+        <v>57144</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219955</v>
+        <v>102613</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Slåttergubbe</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Arnica montana</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Bredhällavägen, Karskruv, Sm</t>
+          <t>Karskruv, norr om Bredhällavägen, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>518109</v>
+        <v>518272</v>
       </c>
       <c r="R6" t="n">
-        <v>6326553</v>
+        <v>6326698</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1225,12 +1233,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2017-06-21</t>
+          <t>2017-04-27</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2017-06-21</t>
+          <t>2017-04-27</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1244,7 +1252,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Vägkant</t>
+          <t>Tallmosse</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1262,7 +1270,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>90949279</v>
+        <v>68354690</v>
       </c>
       <c r="B7" t="n">
         <v>107908</v>
@@ -1300,13 +1308,15 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Bredhällavägen, Karskruv, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>518110</v>
+        <v>518109</v>
       </c>
       <c r="R7" t="n">
         <v>6326553</v>
@@ -1334,11 +1344,6 @@
           <t>Nottebäck</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>G-Upp-0463</t>
-        </is>
-      </c>
       <c r="Y7" t="inlineStr">
         <is>
           <t>2017-06-21</t>
@@ -1366,7 +1371,7 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Sofia Lund</t>
+          <t>Örjan Fritz</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
@@ -1374,60 +1379,58 @@
           <t>Örjan Fritz</t>
         </is>
       </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>68355056</v>
+        <v>90949279</v>
       </c>
       <c r="B8" t="n">
-        <v>97987</v>
+        <v>107908</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>224364</v>
+        <v>219955</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vanlig mattlummer</t>
+          <t>Slåttergubbe</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum subsp. clavatum</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
+          <t>Arnica montana</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Karskruv, norr om Bredhällavägen, Sm</t>
+          <t>Bredhällavägen, Karskruv, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>518186</v>
+        <v>518110</v>
       </c>
       <c r="R8" t="n">
-        <v>6326652</v>
+        <v>6326553</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1452,14 +1455,19 @@
           <t>Nottebäck</t>
         </is>
       </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>G-Upp-0463</t>
+        </is>
+      </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2017-04-27</t>
+          <t>2017-06-21</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2017-04-27</t>
+          <t>2017-06-21</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1473,25 +1481,29 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Gammal grustäkt</t>
+          <t>Vägkant</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
+          <t>Sofia Lund</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
           <t>Örjan Fritz</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>Örjan Fritz</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>68355058</v>
+        <v>68355056</v>
       </c>
       <c r="B9" t="n">
         <v>97987</v>
@@ -1533,10 +1545,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>518188</v>
+        <v>518186</v>
       </c>
       <c r="R9" t="n">
-        <v>6326637</v>
+        <v>6326652</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1600,7 +1612,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>68355070</v>
+        <v>68355058</v>
       </c>
       <c r="B10" t="n">
         <v>97987</v>
@@ -1626,7 +1638,7 @@
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1642,10 +1654,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>518206</v>
+        <v>518188</v>
       </c>
       <c r="R10" t="n">
-        <v>6326644</v>
+        <v>6326637</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1691,7 +1703,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Gammal grustäkt, vägkant</t>
+          <t>Gammal grustäkt</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1709,48 +1721,52 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>68354695</v>
+        <v>68355070</v>
       </c>
       <c r="B11" t="n">
-        <v>102563</v>
+        <v>97987</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>265350</v>
+        <v>224364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vanligt jungfrulin</t>
+          <t>Vanlig mattlummer</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Polygala vulgaris subsp. vulgaris</t>
+          <t>Lycopodium clavatum subsp. clavatum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Bredhällavägen, Karskruv, Sm</t>
+          <t>Karskruv, norr om Bredhällavägen, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>518109</v>
+        <v>518206</v>
       </c>
       <c r="R11" t="n">
-        <v>6326553</v>
+        <v>6326644</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1777,12 +1793,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2017-06-21</t>
+          <t>2017-04-27</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2017-06-21</t>
+          <t>2017-04-27</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1796,7 +1812,7 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Vägkant</t>
+          <t>Gammal grustäkt, vägkant</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1811,6 +1827,111 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>68354695</v>
+      </c>
+      <c r="B12" t="n">
+        <v>102563</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>265350</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Vanligt jungfrulin</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Polygala vulgaris subsp. vulgaris</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Bredhällavägen, Karskruv, Sm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>518109</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6326553</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Uppvidinge</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Nottebäck</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2017-06-21</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2017-06-21</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Vägkant</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Örjan Fritz</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Örjan Fritz</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
